--- a/.ai-context/source-docs/Day-to-day activities-SDD.xlsx
+++ b/.ai-context/source-docs/Day-to-day activities-SDD.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>Day</t>
   </si>
@@ -146,10 +146,19 @@
     <t>Gate 1 peer review of the specification</t>
   </si>
   <si>
+    <t>Gate 1 peer review by Sourav Kumar Maity across five passes, with three revision cycles by the author. BRD and spec reviewed (PASS WITH CONDITIONS); v1.1 addressed all 15 observations (Q12/Q13 added, controlled assumptions for Q07/Q08, AC18/API04 downstream completion, state-model and AC12 fixes). BRD passed Gate 1; spec v1.1 re-review returned six consistency conditions, fixed in v1.2 (plus a self-caught UT12 fix and reviewer guidance). Part 4 returned nine mechanical items (P4-01..P4-09), fixed in v1.2.1 with a self-check against the reviewer's checklist. Final Part 5 review: spec APPROVED.</t>
+  </si>
+  <si>
     <t>1.5-2</t>
   </si>
   <si>
-    <t>Pending</t>
+    <t>BRD.md (Gate 1 PASS); specs/emp-internal-transfer.spec.md (Approved - Gate 1, v1.2.1) with review Parts 1-5 and revision notes v1.1, v1.2, v1.2.1; test_cases/emp-internal-transfer.test_cases.md updated for v1.2.1</t>
+  </si>
+  <si>
+    <t>Carried into Day 5: open Q06/Q11/Q12/Q13; controlled assumptions Q05/Q07/Q08 to validate; contract gaps (pending_resolution entry, pendingWith with several steps, reference-data endpoints, downstream-role mapping); non-blocking editorial fix (Context Q01-Q11 count)</t>
+  </si>
+  <si>
+    <t>Day 5: Technical Plan + Architecture</t>
   </si>
   <si>
     <t>Day 5</t>
@@ -161,16 +170,31 @@
     <t>Technical Plan + Architecture: integration approach, data model, failure handling, ADR candidates</t>
   </si>
   <si>
+    <t>Authored the technical plan from the Gate 1-approved spec: architecture and Laravel/Next.js responsibilities, API01-API04 mapping, logical data model, state model (hr_approved never persisted), auth/RBAC approach, reference-data options, downstream boundaries (human-completed via API04, no system integration), failure/concurrency/idempotency handling, security/observability/performance, testing strategy traced BRD-AC-API-UT, 11 ADR candidates and open decisions. No Laravel/Next.js source exists, so every choice is labelled Fact/Approved/Rule/Proposed/Open/ADR. Raised CR-01 (contradicting approved test cases AUTH-07/STATE-06/STATE-08), CR-02 (reference-data endpoint) and CR-03 (API01 idempotency). No code written.</t>
+  </si>
+  <si>
     <t>3-4</t>
   </si>
   <si>
+    <t>plans/emp-internal-transfer.plan.md (Draft - Technical Review Required); status.md; project_context.md; prompt_history.md</t>
+  </si>
+  <si>
+    <t>Complete - technical review pending</t>
+  </si>
+  <si>
+    <t>No technical reviewer assigned (R-01); ADR-0001 auth, ADR-0002 stack/DB/test frameworks, ADR-0004 role mapping undecided; CR-01 needs author + Gate 1 reviewer agreement; no Laravel/Next.js scaffold yet</t>
+  </si>
+  <si>
+    <t>Assign a technical reviewer and review the plan; decide ADR-0001/0002/0004 and CR-01; then Day 6: Task Decomposition + AI Prompts</t>
+  </si>
+  <si>
+    <t>Day 6</t>
+  </si>
+  <si>
+    <t>Task Decomposition + AI Prompts: task-to-AC mapping, implementation prompts</t>
+  </si>
+  <si>
     <t>Not Started</t>
-  </si>
-  <si>
-    <t>Day 6</t>
-  </si>
-  <si>
-    <t>Task Decomposition + AI Prompts: task-to-AC mapping, implementation prompts</t>
   </si>
   <si>
     <t>Day 7</t>
@@ -1485,7 +1509,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:11">
+    <row r="5" ht="220" customHeight="1" spans="1:11">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -1495,51 +1519,75 @@
       <c r="C5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46295</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="I5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="6" ht="60" customHeight="1" spans="1:11">
+    <row r="6" ht="220" customHeight="1" spans="1:11">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="E6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46295</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:11">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="3" t="s">
@@ -1549,89 +1597,89 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8" ht="60" customHeight="1" spans="1:11">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:11">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
     <row r="10" ht="60" customHeight="1" spans="1:11">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11" ht="60" customHeight="1" spans="1:11">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="3" t="s">
@@ -1641,7 +1689,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
